--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/71.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/71.xlsx
@@ -426,13 +426,13 @@
         <v>-20.05460288949773</v>
       </c>
       <c r="E2">
-        <v>-10.4067387540926</v>
+        <v>-13.14209555131576</v>
       </c>
       <c r="F2">
-        <v>-2.608148878025266</v>
+        <v>-2.862386431088074</v>
       </c>
       <c r="G2">
-        <v>-11.44620573160739</v>
+        <v>-12.74774008928077</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.03135355546543</v>
       </c>
       <c r="E3">
-        <v>-10.45451415487352</v>
+        <v>-13.04255516415316</v>
       </c>
       <c r="F3">
-        <v>-2.225032267700106</v>
+        <v>-2.829667575412298</v>
       </c>
       <c r="G3">
-        <v>-11.47709643203432</v>
+        <v>-12.502067815357</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.91100504915138</v>
       </c>
       <c r="E4">
-        <v>-11.11653177005485</v>
+        <v>-13.59222133920419</v>
       </c>
       <c r="F4">
-        <v>-2.625037632633542</v>
+        <v>-2.95129096259353</v>
       </c>
       <c r="G4">
-        <v>-9.25939177018641</v>
+        <v>-12.55634089892781</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.67090830314789</v>
       </c>
       <c r="E5">
-        <v>-12.17926499322691</v>
+        <v>-15.0402688302669</v>
       </c>
       <c r="F5">
-        <v>-2.210799258985205</v>
+        <v>-2.99545371393898</v>
       </c>
       <c r="G5">
-        <v>-10.1794453442785</v>
+        <v>-11.46311930876752</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.31730944805786</v>
       </c>
       <c r="E6">
-        <v>-10.97350444699659</v>
+        <v>-15.50345020871944</v>
       </c>
       <c r="F6">
-        <v>-2.373634752823115</v>
+        <v>-3.032841248296933</v>
       </c>
       <c r="G6">
-        <v>-10.87998988584368</v>
+        <v>-10.8772520646827</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.84971709643805</v>
       </c>
       <c r="E7">
-        <v>-13.19097589975456</v>
+        <v>-15.12266441483646</v>
       </c>
       <c r="F7">
-        <v>-2.87753230068086</v>
+        <v>-3.027251425062842</v>
       </c>
       <c r="G7">
-        <v>-9.898823641096639</v>
+        <v>-11.12380494371992</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.29469283608236</v>
       </c>
       <c r="E8">
-        <v>-14.50099097458947</v>
+        <v>-16.81380491910492</v>
       </c>
       <c r="F8">
-        <v>-2.363458259279723</v>
+        <v>-3.011392331136246</v>
       </c>
       <c r="G8">
-        <v>-7.216728893181919</v>
+        <v>-10.48118501745537</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.67442215331205</v>
       </c>
       <c r="E9">
-        <v>-15.55817228862813</v>
+        <v>-16.7547490895709</v>
       </c>
       <c r="F9">
-        <v>-2.316148540171037</v>
+        <v>-2.865016497591962</v>
       </c>
       <c r="G9">
-        <v>-7.992641314494143</v>
+        <v>-10.47532204130532</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.03491155123583</v>
       </c>
       <c r="E10">
-        <v>-14.8616748723524</v>
+        <v>-17.22777537051611</v>
       </c>
       <c r="F10">
-        <v>-2.745693486688304</v>
+        <v>-2.761873158799784</v>
       </c>
       <c r="G10">
-        <v>-7.932002051851312</v>
+        <v>-9.616510249144209</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.41765596586623</v>
       </c>
       <c r="E11">
-        <v>-14.72821168639834</v>
+        <v>-17.44997853312448</v>
       </c>
       <c r="F11">
-        <v>-2.531899315332377</v>
+        <v>-2.953799259089207</v>
       </c>
       <c r="G11">
-        <v>-8.786318123170096</v>
+        <v>-9.554027012636006</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.87756316149706</v>
       </c>
       <c r="E12">
-        <v>-16.48277799761823</v>
+        <v>-18.71533832576975</v>
       </c>
       <c r="F12">
-        <v>-1.826233005705145</v>
+        <v>-2.72663937968911</v>
       </c>
       <c r="G12">
-        <v>-6.121838788069838</v>
+        <v>-8.459789084995162</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.4608229134416</v>
       </c>
       <c r="E13">
-        <v>-17.07334534990654</v>
+        <v>-20.26722825430236</v>
       </c>
       <c r="F13">
-        <v>-2.354816730533718</v>
+        <v>-2.553146939214185</v>
       </c>
       <c r="G13">
-        <v>-6.425058275102765</v>
+        <v>-8.231636218065209</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.20954980009043</v>
       </c>
       <c r="E14">
-        <v>-19.10102845700304</v>
+        <v>-20.56647434520322</v>
       </c>
       <c r="F14">
-        <v>-1.841253791820109</v>
+        <v>-2.385353666470519</v>
       </c>
       <c r="G14">
-        <v>-5.679000353463689</v>
+        <v>-7.276530587803314</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.15227268428297</v>
       </c>
       <c r="E15">
-        <v>-18.86914341696627</v>
+        <v>-21.59834601801301</v>
       </c>
       <c r="F15">
-        <v>-1.529537481411849</v>
+        <v>-2.149775917523173</v>
       </c>
       <c r="G15">
-        <v>-5.540083241544791</v>
+        <v>-7.642968252454163</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.29296516752204</v>
       </c>
       <c r="E16">
-        <v>-18.95128087851739</v>
+        <v>-21.34155889940806</v>
       </c>
       <c r="F16">
-        <v>-1.413307594390245</v>
+        <v>-2.101728951425997</v>
       </c>
       <c r="G16">
-        <v>-3.990344042610084</v>
+        <v>-7.569189434565965</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.62388829475418</v>
       </c>
       <c r="E17">
-        <v>-19.23402521013431</v>
+        <v>-22.54955198332417</v>
       </c>
       <c r="F17">
-        <v>-1.384996481664766</v>
+        <v>-1.693677653909168</v>
       </c>
       <c r="G17">
-        <v>-3.965190517602702</v>
+        <v>-7.271726986225832</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.10905190266766</v>
       </c>
       <c r="E18">
-        <v>-21.44792822537423</v>
+        <v>-23.5330912530501</v>
       </c>
       <c r="F18">
-        <v>-0.651956771212025</v>
+        <v>-1.33180701073101</v>
       </c>
       <c r="G18">
-        <v>-4.339345063905592</v>
+        <v>-7.095539752625819</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-16.71213421647346</v>
       </c>
       <c r="E19">
-        <v>-21.94822497679364</v>
+        <v>-24.26050003290218</v>
       </c>
       <c r="F19">
-        <v>-0.8777125678643771</v>
+        <v>-1.203799395976402</v>
       </c>
       <c r="G19">
-        <v>-5.088726773266097</v>
+        <v>-6.604632196789452</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.37285316720462</v>
       </c>
       <c r="E20">
-        <v>-24.88813294494327</v>
+        <v>-25.1433713254376</v>
       </c>
       <c r="F20">
-        <v>-0.5846270687124813</v>
+        <v>-0.8485324977333617</v>
       </c>
       <c r="G20">
-        <v>-4.442577805456685</v>
+        <v>-7.23062656335578</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-18.04027507793588</v>
       </c>
       <c r="E21">
-        <v>-23.33850725341451</v>
+        <v>-24.89331804768205</v>
       </c>
       <c r="F21">
-        <v>0.0982740479510144</v>
+        <v>-0.949665388838945</v>
       </c>
       <c r="G21">
-        <v>-4.701068511708519</v>
+        <v>-7.093255476203722</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-18.64692216691897</v>
       </c>
       <c r="E22">
-        <v>-25.13506157563352</v>
+        <v>-26.16268553982412</v>
       </c>
       <c r="F22">
-        <v>-0.1522267397577645</v>
+        <v>-0.6379242274086014</v>
       </c>
       <c r="G22">
-        <v>-4.964240329352882</v>
+        <v>-6.616384633453865</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-19.14555520986646</v>
       </c>
       <c r="E23">
-        <v>-23.70611065946116</v>
+        <v>-25.44322423185549</v>
       </c>
       <c r="F23">
-        <v>0.05549218506603113</v>
+        <v>-0.236815477094636</v>
       </c>
       <c r="G23">
-        <v>-5.220360684998598</v>
+        <v>-7.419370696186248</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-19.48458209522278</v>
       </c>
       <c r="E24">
-        <v>-24.76666115816152</v>
+        <v>-26.9135246441919</v>
       </c>
       <c r="F24">
-        <v>0.06032819396357465</v>
+        <v>-0.4004859652745679</v>
       </c>
       <c r="G24">
-        <v>-5.39591229385507</v>
+        <v>-7.596369013443382</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-19.64250348290386</v>
       </c>
       <c r="E25">
-        <v>-23.92693263749718</v>
+        <v>-25.88686071649093</v>
       </c>
       <c r="F25">
-        <v>-0.1002963872762635</v>
+        <v>-0.1863952383884385</v>
       </c>
       <c r="G25">
-        <v>-5.34348980524071</v>
+        <v>-7.430259080464911</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-19.60305984235728</v>
       </c>
       <c r="E26">
-        <v>-24.73486221367966</v>
+        <v>-26.59093426978149</v>
       </c>
       <c r="F26">
-        <v>-0.01245713625080672</v>
+        <v>-0.339742611994683</v>
       </c>
       <c r="G26">
-        <v>-5.382051039682142</v>
+        <v>-8.176661298840072</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-19.38298282267033</v>
       </c>
       <c r="E27">
-        <v>-24.2203052976101</v>
+        <v>-27.26655089240785</v>
       </c>
       <c r="F27">
-        <v>-0.3734422546753725</v>
+        <v>-0.6174826050097181</v>
       </c>
       <c r="G27">
-        <v>-5.125295059292887</v>
+        <v>-8.135031188683737</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-19.00620512898299</v>
       </c>
       <c r="E28">
-        <v>-25.06852923551283</v>
+        <v>-26.47417662444172</v>
       </c>
       <c r="F28">
-        <v>-0.3478862919316049</v>
+        <v>-0.5278449683527835</v>
       </c>
       <c r="G28">
-        <v>-5.717899263550125</v>
+        <v>-8.172576085644611</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-18.52172714242872</v>
       </c>
       <c r="E29">
-        <v>-24.11485072339348</v>
+        <v>-26.31260972879606</v>
       </c>
       <c r="F29">
-        <v>-0.4329770199145729</v>
+        <v>-0.3240491915486464</v>
       </c>
       <c r="G29">
-        <v>-5.408128206894981</v>
+        <v>-7.928628605946796</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-17.97540704898545</v>
       </c>
       <c r="E30">
-        <v>-24.12903843245951</v>
+        <v>-25.8995404437124</v>
       </c>
       <c r="F30">
-        <v>-0.2725686425668655</v>
+        <v>-0.2580473619957901</v>
       </c>
       <c r="G30">
-        <v>-6.82099290050852</v>
+        <v>-7.687865871057759</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-17.42193365107666</v>
       </c>
       <c r="E31">
-        <v>-22.60332308369125</v>
+        <v>-25.35535825068466</v>
       </c>
       <c r="F31">
-        <v>-0.5711213665772381</v>
+        <v>-0.4333067101408871</v>
       </c>
       <c r="G31">
-        <v>-4.858494883737482</v>
+        <v>-8.624955512494939</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-16.90140158199429</v>
       </c>
       <c r="E32">
-        <v>-23.73004364459169</v>
+        <v>-25.62386506002146</v>
       </c>
       <c r="F32">
-        <v>-0.4297977458226284</v>
+        <v>-0.8311417524789889</v>
       </c>
       <c r="G32">
-        <v>-6.128804175884465</v>
+        <v>-7.887458661620419</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-16.4500337475991</v>
       </c>
       <c r="E33">
-        <v>-22.74910371894617</v>
+        <v>-24.26196725848067</v>
       </c>
       <c r="F33">
-        <v>-0.818506664484088</v>
+        <v>-0.9577792475493662</v>
       </c>
       <c r="G33">
-        <v>-5.105461580967113</v>
+        <v>-7.18124977663755</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-16.08862347123947</v>
       </c>
       <c r="E34">
-        <v>-22.37152408466062</v>
+        <v>-24.32703237302288</v>
       </c>
       <c r="F34">
-        <v>-0.7476257509287427</v>
+        <v>-0.7141928425517547</v>
       </c>
       <c r="G34">
-        <v>-3.822009423029223</v>
+        <v>-7.18297788140905</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.82899027109639</v>
       </c>
       <c r="E35">
-        <v>-21.55303410709226</v>
+        <v>-23.97468992438208</v>
       </c>
       <c r="F35">
-        <v>0.02846504181489166</v>
+        <v>-0.879935905973491</v>
       </c>
       <c r="G35">
-        <v>-4.879957150468577</v>
+        <v>-7.669591659680982</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-15.67105248653915</v>
       </c>
       <c r="E36">
-        <v>-20.92051950007091</v>
+        <v>-23.29018390727866</v>
       </c>
       <c r="F36">
-        <v>-0.1915302879183926</v>
+        <v>-0.6417256054200483</v>
       </c>
       <c r="G36">
-        <v>-3.969070476974728</v>
+        <v>-6.748203935736565</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.60194663404577</v>
       </c>
       <c r="E37">
-        <v>-21.66102915522718</v>
+        <v>-23.10154126554113</v>
       </c>
       <c r="F37">
-        <v>-0.2383844049555383</v>
+        <v>-0.7690407050259156</v>
       </c>
       <c r="G37">
-        <v>-4.523994051903982</v>
+        <v>-7.123388061702168</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-15.60586237973416</v>
       </c>
       <c r="E38">
-        <v>-20.63242251217692</v>
+        <v>-23.00878453244202</v>
       </c>
       <c r="F38">
-        <v>-0.1727429152228999</v>
+        <v>-0.5979124251185797</v>
       </c>
       <c r="G38">
-        <v>-4.370490676339055</v>
+        <v>-6.501790099611992</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-15.65436882426779</v>
       </c>
       <c r="E39">
-        <v>-19.64342643127176</v>
+        <v>-22.97669576562367</v>
       </c>
       <c r="F39">
-        <v>-0.624150962602254</v>
+        <v>-0.9989739584905856</v>
       </c>
       <c r="G39">
-        <v>-5.48648550926399</v>
+        <v>-6.384851699528316</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-15.72643149246743</v>
       </c>
       <c r="E40">
-        <v>-19.77671753521352</v>
+        <v>-22.2883269601917</v>
       </c>
       <c r="F40">
-        <v>-0.50371048407222</v>
+        <v>-0.734738010875988</v>
       </c>
       <c r="G40">
-        <v>-2.676832131175613</v>
+        <v>-6.799868309422431</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-15.79157190647331</v>
       </c>
       <c r="E41">
-        <v>-19.72575861720521</v>
+        <v>-21.71444703462166</v>
       </c>
       <c r="F41">
-        <v>-0.1527527530585422</v>
+        <v>-1.004800694801877</v>
       </c>
       <c r="G41">
-        <v>-3.443620688981605</v>
+        <v>-6.23048427157764</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-15.83671549166763</v>
       </c>
       <c r="E42">
-        <v>-18.91209599292903</v>
+        <v>-21.25501070417347</v>
       </c>
       <c r="F42">
-        <v>-0.5562886198627102</v>
+        <v>-1.168590467887812</v>
       </c>
       <c r="G42">
-        <v>-3.660507769441417</v>
+        <v>-6.279142669913848</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-15.84153089176708</v>
       </c>
       <c r="E43">
-        <v>-19.26666192230759</v>
+        <v>-21.42649495789593</v>
       </c>
       <c r="F43">
-        <v>-0.5494529320548086</v>
+        <v>-1.294351550246028</v>
       </c>
       <c r="G43">
-        <v>-3.003573044265061</v>
+        <v>-5.715154821298069</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-15.8055448942653</v>
       </c>
       <c r="E44">
-        <v>-18.90048045709935</v>
+        <v>-20.30295338574887</v>
       </c>
       <c r="F44">
-        <v>-0.5331282956478388</v>
+        <v>-0.7409855578279019</v>
       </c>
       <c r="G44">
-        <v>-3.651519638302296</v>
+        <v>-5.488210303489951</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-15.71971213448085</v>
       </c>
       <c r="E45">
-        <v>-18.2323675159037</v>
+        <v>-20.04307784787069</v>
       </c>
       <c r="F45">
-        <v>-0.3020576937391251</v>
+        <v>-0.9227136270214603</v>
       </c>
       <c r="G45">
-        <v>-4.312817662499412</v>
+        <v>-5.807489246933882</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-15.59443531020159</v>
       </c>
       <c r="E46">
-        <v>-16.89177165609498</v>
+        <v>-19.66841002237208</v>
       </c>
       <c r="F46">
-        <v>-0.7178335172870586</v>
+        <v>-1.241375798102194</v>
       </c>
       <c r="G46">
-        <v>-3.23464581236065</v>
+        <v>-5.249874198481201</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-15.43222286883769</v>
       </c>
       <c r="E47">
-        <v>-15.83160607768527</v>
+        <v>-19.36358485149376</v>
       </c>
       <c r="F47">
-        <v>-0.314845201336141</v>
+        <v>-1.028379344555162</v>
       </c>
       <c r="G47">
-        <v>-3.107911508026271</v>
+        <v>-5.615437879109682</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-15.25262299250036</v>
       </c>
       <c r="E48">
-        <v>-15.71564544377086</v>
+        <v>-19.31133078991925</v>
       </c>
       <c r="F48">
-        <v>-0.213021451816623</v>
+        <v>-1.293253963437318</v>
       </c>
       <c r="G48">
-        <v>-4.211048182076676</v>
+        <v>-6.025041747047088</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-15.06713168048984</v>
       </c>
       <c r="E49">
-        <v>-15.28142365659737</v>
+        <v>-18.66740442839857</v>
       </c>
       <c r="F49">
-        <v>-0.591751028376557</v>
+        <v>-1.163936699818885</v>
       </c>
       <c r="G49">
-        <v>-3.798425096607455</v>
+        <v>-6.420575796442591</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-14.89917730386976</v>
       </c>
       <c r="E50">
-        <v>-14.48752329289066</v>
+        <v>-18.128045060189</v>
       </c>
       <c r="F50">
-        <v>-0.6719933219509395</v>
+        <v>-1.237064145770622</v>
       </c>
       <c r="G50">
-        <v>-3.853251041283325</v>
+        <v>-6.201245533374797</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-14.7636052471857</v>
       </c>
       <c r="E51">
-        <v>-14.34162038883752</v>
+        <v>-17.76977031059815</v>
       </c>
       <c r="F51">
-        <v>-1.512144251055268</v>
+        <v>-1.263932242480424</v>
       </c>
       <c r="G51">
-        <v>-4.715889824087836</v>
+        <v>-6.407257471738103</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-14.6773788437768</v>
       </c>
       <c r="E52">
-        <v>-13.30449568617884</v>
+        <v>-17.66591881618024</v>
       </c>
       <c r="F52">
-        <v>-0.8876181852670536</v>
+        <v>-1.536033538584603</v>
       </c>
       <c r="G52">
-        <v>-4.688458643749435</v>
+        <v>-6.285548575532338</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-14.64855548310844</v>
       </c>
       <c r="E53">
-        <v>-12.38805028735056</v>
+        <v>-16.47267044363311</v>
       </c>
       <c r="F53">
-        <v>-0.6723495199341433</v>
+        <v>-1.231767564597122</v>
       </c>
       <c r="G53">
-        <v>-4.547826669241195</v>
+        <v>-7.024975474456253</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-14.68061740154266</v>
       </c>
       <c r="E54">
-        <v>-12.77218715199921</v>
+        <v>-16.19364398917649</v>
       </c>
       <c r="F54">
-        <v>-0.6010718183928571</v>
+        <v>-1.096465346493462</v>
       </c>
       <c r="G54">
-        <v>-4.611932073063643</v>
+        <v>-6.7938298743588</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-14.77473006765634</v>
       </c>
       <c r="E55">
-        <v>-12.10954913587883</v>
+        <v>-15.98086005250408</v>
       </c>
       <c r="F55">
-        <v>-0.2208536656100923</v>
+        <v>-1.533451517390077</v>
       </c>
       <c r="G55">
-        <v>-5.030669736143897</v>
+        <v>-6.934998157244402</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-14.92127674827064</v>
       </c>
       <c r="E56">
-        <v>-11.41143505438236</v>
+        <v>-15.28912659088442</v>
       </c>
       <c r="F56">
-        <v>-0.6156204350882247</v>
+        <v>-1.430926140680388</v>
       </c>
       <c r="G56">
-        <v>-5.99155226837182</v>
+        <v>-7.597401903651635</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-15.11484146187702</v>
       </c>
       <c r="E57">
-        <v>-12.94055581560439</v>
+        <v>-16.15175107613154</v>
       </c>
       <c r="F57">
-        <v>-0.6971342726259044</v>
+        <v>-1.351730075135741</v>
       </c>
       <c r="G57">
-        <v>-5.6129020012266</v>
+        <v>-7.558794321572654</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-15.3381856717873</v>
       </c>
       <c r="E58">
-        <v>-12.64638614406613</v>
+        <v>-16.23011179036026</v>
       </c>
       <c r="F58">
-        <v>-1.042348932435973</v>
+        <v>-1.350497464440375</v>
       </c>
       <c r="G58">
-        <v>-6.077993922947731</v>
+        <v>-7.776317026776007</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-15.58571551765529</v>
       </c>
       <c r="E59">
-        <v>-10.786007509183</v>
+        <v>-15.19625211746111</v>
       </c>
       <c r="F59">
-        <v>-0.4586762902190248</v>
+        <v>-1.229854035896655</v>
       </c>
       <c r="G59">
-        <v>-5.905729685811754</v>
+        <v>-7.98942677477551</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-15.83945200134338</v>
       </c>
       <c r="E60">
-        <v>-11.3856001101686</v>
+        <v>-14.55946715945051</v>
       </c>
       <c r="F60">
-        <v>-0.7736108079871604</v>
+        <v>-1.939149423115552</v>
       </c>
       <c r="G60">
-        <v>-6.238429580871891</v>
+        <v>-8.455200668877731</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.09706867418447</v>
       </c>
       <c r="E61">
-        <v>-10.39908563301963</v>
+        <v>-14.74843585131659</v>
       </c>
       <c r="F61">
-        <v>-0.6251367198115855</v>
+        <v>-1.398824418719699</v>
       </c>
       <c r="G61">
-        <v>-6.789658586979319</v>
+        <v>-8.301160984935443</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-16.34384415028097</v>
       </c>
       <c r="E62">
-        <v>-10.07601524036442</v>
+        <v>-14.7174475036821</v>
       </c>
       <c r="F62">
-        <v>-0.9749430201353719</v>
+        <v>-1.486977620990816</v>
       </c>
       <c r="G62">
-        <v>-7.228590577849128</v>
+        <v>-8.322623251666538</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.58200945560727</v>
       </c>
       <c r="E63">
-        <v>-10.58201334055948</v>
+        <v>-14.36461597984847</v>
       </c>
       <c r="F63">
-        <v>-0.9535520886928802</v>
+        <v>-1.590270894282901</v>
       </c>
       <c r="G63">
-        <v>-7.388774634312304</v>
+        <v>-8.558612179887945</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.80012700164643</v>
       </c>
       <c r="E64">
-        <v>-11.27687597771844</v>
+        <v>-14.64325751401444</v>
       </c>
       <c r="F64">
-        <v>-1.091534075344597</v>
+        <v>-1.443432003360452</v>
       </c>
       <c r="G64">
-        <v>-6.950193561269657</v>
+        <v>-9.257213431221569</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-17.00275789544995</v>
       </c>
       <c r="E65">
-        <v>-9.729605092673664</v>
+        <v>-14.23196791921579</v>
       </c>
       <c r="F65">
-        <v>-0.9987113660238981</v>
+        <v>-1.378402677138482</v>
       </c>
       <c r="G65">
-        <v>-6.994571424223587</v>
+        <v>-9.130032203239388</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-17.18267390161582</v>
       </c>
       <c r="E66">
-        <v>-10.41782445846337</v>
+        <v>-13.9849532475194</v>
       </c>
       <c r="F66">
-        <v>-0.5511386597195056</v>
+        <v>-1.619363985836622</v>
       </c>
       <c r="G66">
-        <v>-7.311023161776981</v>
+        <v>-8.316233898775744</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-17.34676215736864</v>
       </c>
       <c r="E67">
-        <v>-9.656021918523029</v>
+        <v>-14.34425143223598</v>
       </c>
       <c r="F67">
-        <v>-0.580202758414129</v>
+        <v>-1.621735601710837</v>
       </c>
       <c r="G67">
-        <v>-6.062669407646444</v>
+        <v>-8.999894658090637</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-17.49186672183727</v>
       </c>
       <c r="E68">
-        <v>-11.25631670572362</v>
+        <v>-13.49628561735169</v>
       </c>
       <c r="F68">
-        <v>-0.7870825470588888</v>
+        <v>-1.260305649990968</v>
       </c>
       <c r="G68">
-        <v>-8.069800199377937</v>
+        <v>-9.32747644974706</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-17.62529369792743</v>
       </c>
       <c r="E69">
-        <v>-9.364895381517917</v>
+        <v>-14.62458208720681</v>
       </c>
       <c r="F69">
-        <v>-0.9004901863391551</v>
+        <v>-1.689204469934051</v>
       </c>
       <c r="G69">
-        <v>-7.928943107773026</v>
+        <v>-9.247199030965273</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-17.74641422276801</v>
       </c>
       <c r="E70">
-        <v>-10.97312858365395</v>
+        <v>-13.47429081909644</v>
       </c>
       <c r="F70">
-        <v>-0.6247333048864221</v>
+        <v>-1.857576771492273</v>
       </c>
       <c r="G70">
-        <v>-7.760495929643829</v>
+        <v>-9.17758156881994</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-17.86027730113619</v>
       </c>
       <c r="E71">
-        <v>-10.39207555525576</v>
+        <v>-13.24979624864019</v>
       </c>
       <c r="F71">
-        <v>-0.9347489770167343</v>
+        <v>-1.606909481935532</v>
       </c>
       <c r="G71">
-        <v>-7.338570211209256</v>
+        <v>-9.640885795949863</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-17.96708066686304</v>
       </c>
       <c r="E72">
-        <v>-11.32431627142279</v>
+        <v>-13.68049941150971</v>
       </c>
       <c r="F72">
-        <v>-1.58982109078318</v>
+        <v>-1.276079422075076</v>
       </c>
       <c r="G72">
-        <v>-7.826826020068667</v>
+        <v>-9.775850116494871</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.0670986460224</v>
       </c>
       <c r="E73">
-        <v>-10.438859220229</v>
+        <v>-14.14086860760349</v>
       </c>
       <c r="F73">
-        <v>-0.8743957847835679</v>
+        <v>-1.5244629027023</v>
       </c>
       <c r="G73">
-        <v>-6.938603341336668</v>
+        <v>-9.757496452025151</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.16005323420459</v>
       </c>
       <c r="E74">
-        <v>-11.24096517883762</v>
+        <v>-14.72064913480552</v>
       </c>
       <c r="F74">
-        <v>-1.402837858786262</v>
+        <v>-1.803350184570212</v>
       </c>
       <c r="G74">
-        <v>-8.095605901856555</v>
+        <v>-9.353646312235</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.24171980122615</v>
       </c>
       <c r="E75">
-        <v>-10.49644782418455</v>
+        <v>-15.11356218208104</v>
       </c>
       <c r="F75">
-        <v>-0.6868708005052186</v>
+        <v>-1.592213415842465</v>
       </c>
       <c r="G75">
-        <v>-7.750325933747188</v>
+        <v>-10.19431962538645</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-18.31364449904725</v>
       </c>
       <c r="E76">
-        <v>-12.8652291789608</v>
+        <v>-15.95598514477994</v>
       </c>
       <c r="F76">
-        <v>-1.149587719667592</v>
+        <v>-1.456888003451527</v>
       </c>
       <c r="G76">
-        <v>-7.911777929151905</v>
+        <v>-9.09963146355226</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-18.36918164162828</v>
       </c>
       <c r="E77">
-        <v>-11.81940074925937</v>
+        <v>-15.55521519510112</v>
       </c>
       <c r="F77">
-        <v>-0.6905147887101336</v>
+        <v>-1.689904440389417</v>
       </c>
       <c r="G77">
-        <v>-7.501429188468163</v>
+        <v>-9.076785388785749</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-18.41186109846176</v>
       </c>
       <c r="E78">
-        <v>-11.7747862233358</v>
+        <v>-15.3328671213245</v>
       </c>
       <c r="F78">
-        <v>-0.8190161104368098</v>
+        <v>-1.89443580744724</v>
       </c>
       <c r="G78">
-        <v>-7.438310327216418</v>
+        <v>-9.425749994080325</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-18.43403130660865</v>
       </c>
       <c r="E79">
-        <v>-12.32541243487646</v>
+        <v>-15.79653304649587</v>
       </c>
       <c r="F79">
-        <v>-1.53841178139804</v>
+        <v>-2.031929057331304</v>
       </c>
       <c r="G79">
-        <v>-8.344714522050095</v>
+        <v>-9.258312532340607</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-18.4413254729411</v>
       </c>
       <c r="E80">
-        <v>-12.09586861590166</v>
+        <v>-16.34309721685164</v>
       </c>
       <c r="F80">
-        <v>-1.239657764108788</v>
+        <v>-1.655485774803097</v>
       </c>
       <c r="G80">
-        <v>-7.882876866594067</v>
+        <v>-9.338047021653953</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-18.4267228256364</v>
       </c>
       <c r="E81">
-        <v>-12.11963404749391</v>
+        <v>-17.04294570389305</v>
       </c>
       <c r="F81">
-        <v>-1.139187566925444</v>
+        <v>-1.886985471026461</v>
       </c>
       <c r="G81">
-        <v>-8.333670542131086</v>
+        <v>-9.24626214657766</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-18.39900297771365</v>
       </c>
       <c r="E82">
-        <v>-14.18778812679696</v>
+        <v>-17.76400556318638</v>
       </c>
       <c r="F82">
-        <v>-1.038632876267015</v>
+        <v>-2.205435580052078</v>
       </c>
       <c r="G82">
-        <v>-7.263116257278187</v>
+        <v>-9.720676564537378</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-18.35147518955581</v>
       </c>
       <c r="E83">
-        <v>-15.89572021268587</v>
+        <v>-18.61438052624275</v>
       </c>
       <c r="F83">
-        <v>-0.9466609002689912</v>
+        <v>-1.685955612980272</v>
       </c>
       <c r="G83">
-        <v>-6.961316994281608</v>
+        <v>-9.522778773290826</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-18.2927317562941</v>
       </c>
       <c r="E84">
-        <v>-15.90218687356882</v>
+        <v>-19.30583322247394</v>
       </c>
       <c r="F84">
-        <v>-1.12156570716569</v>
+        <v>-1.952005685207</v>
       </c>
       <c r="G84">
-        <v>-7.27954649478959</v>
+        <v>-9.455770021030437</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-18.21486337686152</v>
       </c>
       <c r="E85">
-        <v>-16.90076973394823</v>
+        <v>-19.66981384931445</v>
       </c>
       <c r="F85">
-        <v>-1.335954646316827</v>
+        <v>-2.234838481014446</v>
       </c>
       <c r="G85">
-        <v>-7.640293331658432</v>
+        <v>-9.310543009313689</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-18.12614153867299</v>
       </c>
       <c r="E86">
-        <v>-17.99916468993069</v>
+        <v>-20.919396438517</v>
       </c>
       <c r="F86">
-        <v>-1.90296053638945</v>
+        <v>-2.314083420235858</v>
       </c>
       <c r="G86">
-        <v>-6.999103561066849</v>
+        <v>-9.318398933878379</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-18.0198458899604</v>
       </c>
       <c r="E87">
-        <v>-19.07799663820003</v>
+        <v>-21.75045293145665</v>
       </c>
       <c r="F87">
-        <v>-1.923590198188768</v>
+        <v>-1.987724887615715</v>
       </c>
       <c r="G87">
-        <v>-7.988178699107205</v>
+        <v>-9.566805718417593</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-17.90514487937046</v>
       </c>
       <c r="E88">
-        <v>-19.93360198873526</v>
+        <v>-22.66861462193384</v>
       </c>
       <c r="F88">
-        <v>-2.087753564973366</v>
+        <v>-2.013941059179513</v>
       </c>
       <c r="G88">
-        <v>-7.061553692119661</v>
+        <v>-9.786361098582057</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-17.7781160922714</v>
       </c>
       <c r="E89">
-        <v>-22.12273877962723</v>
+        <v>-23.71759939801862</v>
       </c>
       <c r="F89">
-        <v>-1.861808072185773</v>
+        <v>-2.249233849740296</v>
       </c>
       <c r="G89">
-        <v>-7.101068363676402</v>
+        <v>-8.779594405179836</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.64888620715416</v>
       </c>
       <c r="E90">
-        <v>-22.99403529259904</v>
+        <v>-25.71547156072262</v>
       </c>
       <c r="F90">
-        <v>-1.663808382099024</v>
+        <v>-1.795769794467194</v>
       </c>
       <c r="G90">
-        <v>-7.164025008196722</v>
+        <v>-9.081062613622489</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.51755938789473</v>
       </c>
       <c r="E91">
-        <v>-25.41048789325404</v>
+        <v>-27.5826700774613</v>
       </c>
       <c r="F91">
-        <v>-1.815463401101349</v>
+        <v>-2.087263171470909</v>
       </c>
       <c r="G91">
-        <v>-7.481400387955572</v>
+        <v>-9.522974095477641</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.39466524972411</v>
       </c>
       <c r="E92">
-        <v>-27.91660427926092</v>
+        <v>-29.54882480821558</v>
       </c>
       <c r="F92">
-        <v>-1.654414695751278</v>
+        <v>-2.284191782505838</v>
       </c>
       <c r="G92">
-        <v>-7.965107507244024</v>
+        <v>-9.580968232234595</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.2831500307285</v>
       </c>
       <c r="E93">
-        <v>-28.33784745992842</v>
+        <v>-30.90692774853795</v>
       </c>
       <c r="F93">
-        <v>-1.885757830535512</v>
+        <v>-2.00474949447805</v>
       </c>
       <c r="G93">
-        <v>-8.268578595737935</v>
+        <v>-10.16398840715564</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.18840045567244</v>
       </c>
       <c r="E94">
-        <v>-28.75431762899184</v>
+        <v>-33.21815446291372</v>
       </c>
       <c r="F94">
-        <v>-1.722728498725347</v>
+        <v>-1.944482452454775</v>
       </c>
       <c r="G94">
-        <v>-7.501584784108508</v>
+        <v>-10.09547335667489</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.11313778219965</v>
       </c>
       <c r="E95">
-        <v>-31.10300388035906</v>
+        <v>-34.76953493812045</v>
       </c>
       <c r="F95">
-        <v>-1.515731910276793</v>
+        <v>-2.159073513252195</v>
       </c>
       <c r="G95">
-        <v>-7.645583583430187</v>
+        <v>-10.50753695994797</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.05803532302531</v>
       </c>
       <c r="E96">
-        <v>-35.11661303572733</v>
+        <v>-36.51157549023513</v>
       </c>
       <c r="F96">
-        <v>-2.008398452887382</v>
+        <v>-1.838403379587076</v>
       </c>
       <c r="G96">
-        <v>-6.722891504543297</v>
+        <v>-9.472693529827191</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.02476041233609</v>
       </c>
       <c r="E97">
-        <v>-37.39804691960664</v>
+        <v>-38.47143337788175</v>
       </c>
       <c r="F97">
-        <v>-2.049358735853609</v>
+        <v>-1.976788781163956</v>
       </c>
       <c r="G97">
-        <v>-8.284800268880364</v>
+        <v>-10.09111336819967</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-17.01457651513932</v>
       </c>
       <c r="E98">
-        <v>-39.98102509494571</v>
+        <v>-41.87531520743527</v>
       </c>
       <c r="F98">
-        <v>-2.355674919163019</v>
+        <v>-1.938046866102425</v>
       </c>
       <c r="G98">
-        <v>-7.864728455947783</v>
+        <v>-10.80133463437613</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-17.02833350924837</v>
       </c>
       <c r="E99">
-        <v>-40.68526167330054</v>
+        <v>-42.54320398916754</v>
       </c>
       <c r="F99">
-        <v>-2.307723215317164</v>
+        <v>-1.984124802883148</v>
       </c>
       <c r="G99">
-        <v>-7.863136083543393</v>
+        <v>-10.47167382012105</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-17.07269712611931</v>
       </c>
       <c r="E100">
-        <v>-42.21638402003397</v>
+        <v>-46.65420477078178</v>
       </c>
       <c r="F100">
-        <v>-2.579368909349803</v>
+        <v>-2.568141217572258</v>
       </c>
       <c r="G100">
-        <v>-8.962369624402998</v>
+        <v>-10.09252697114494</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-17.14171546901761</v>
       </c>
       <c r="E101">
-        <v>-47.49254757839977</v>
+        <v>-48.05474177679302</v>
       </c>
       <c r="F101">
-        <v>-2.269798898882197</v>
+        <v>-2.376162101769056</v>
       </c>
       <c r="G101">
-        <v>-8.869760423487426</v>
+        <v>-10.58894327475865</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-17.26001411619333</v>
       </c>
       <c r="E102">
-        <v>-48.97669493213313</v>
+        <v>-50.99377008886666</v>
       </c>
       <c r="F102">
-        <v>-2.157371218239442</v>
+        <v>-2.428554683261319</v>
       </c>
       <c r="G102">
-        <v>-8.62323071826898</v>
+        <v>-10.73138280713133</v>
       </c>
     </row>
   </sheetData>
